--- a/Elli/results_week_v5_resources.xlsx
+++ b/Elli/results_week_v5_resources.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="139">
   <si>
     <t>student_id</t>
   </si>
@@ -326,19 +326,52 @@
     <t>https://youtu.be/K5KVEU3aaeQ</t>
   </si>
   <si>
+    <t>Ποια είναι η τελευταία μεταβλητή ή συνάρτηση πριν από το runtime error;</t>
+  </si>
+  <si>
+    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 1;</t>
+  </si>
+  <si>
+    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 10;</t>
+  </si>
+  <si>
     <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 23;</t>
   </si>
   <si>
     <t>beginner</t>
   </si>
   <si>
+    <t>Δοκίμασε τον κώδικα με μία πολύ μικρή είσοδο και κατέγραψε τις τιμές.</t>
+  </si>
+  <si>
     <t>Διόρθωσε πρώτα μία μικρή εκδοχή του ίδιου συντακτικού λάθους.</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
-    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-3.6-flash\nPlease retry in 531.266211ms.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '0s'}]}}</t>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 4.204584756s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '4s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 3.724205364s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-3.6-flash', 'location': 'global'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '3s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 3.295090872s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '3s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 2.767303624s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 2.333938639s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-3.6-flash', 'location': 'global'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 1.934125925s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '1s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 1.532296688s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '1s'}]}}</t>
+  </si>
+  <si>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 20, model: gemini-3.6-flash\nPlease retry in 1.100196115s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '20'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '1s'}]}}</t>
   </si>
   <si>
     <t>Ομάδα υψηλής ανάγκης υποστήριξης</t>
@@ -1086,22 +1119,22 @@
         <v>102</v>
       </c>
       <c r="BC2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="BD2" t="s">
         <v>103</v>
       </c>
       <c r="BE2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BG2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BI2" t="b">
         <v>1</v>
@@ -1110,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="BK2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:63">
@@ -1274,22 +1307,22 @@
         <v>102</v>
       </c>
       <c r="BC3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BD3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BG3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BI3" t="b">
         <v>1</v>
@@ -1298,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="BK3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:63">
@@ -1465,19 +1498,19 @@
         <v>87</v>
       </c>
       <c r="BD4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BE4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BG4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="BI4" t="b">
         <v>1</v>
@@ -1486,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="BK4" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:63">
@@ -1650,22 +1683,22 @@
         <v>102</v>
       </c>
       <c r="BC5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BD5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BG5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="BI5" t="b">
         <v>1</v>
@@ -1674,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="BK5" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:63">
@@ -1826,22 +1859,22 @@
         <v>102</v>
       </c>
       <c r="BC6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="BD6" t="s">
         <v>103</v>
       </c>
       <c r="BE6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BG6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="BI6" t="b">
         <v>1</v>
@@ -1850,7 +1883,7 @@
         <v>2</v>
       </c>
       <c r="BK6" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:63">
@@ -2014,22 +2047,22 @@
         <v>102</v>
       </c>
       <c r="BC7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BD7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BE7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BG7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="BI7" t="b">
         <v>1</v>
@@ -2038,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="BK7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:63">
@@ -2190,22 +2223,22 @@
         <v>102</v>
       </c>
       <c r="BC8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BD8" t="s">
         <v>103</v>
       </c>
       <c r="BE8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BG8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH8" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="BI8" t="b">
         <v>1</v>
@@ -2214,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="BK8" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:63">
@@ -2381,19 +2414,19 @@
         <v>87</v>
       </c>
       <c r="BD9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BE9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BF9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BG9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH9" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="BI9" t="b">
         <v>1</v>
@@ -2402,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="BK9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2427,31 +2460,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -2467,7 +2500,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -2475,7 +2508,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B7">
         <v>11.88</v>
@@ -2483,7 +2516,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2491,7 +2524,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -2499,7 +2532,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -2507,31 +2540,31 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Elli/results_week_v5_resources.xlsx
+++ b/Elli/results_week_v5_resources.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slabr\source\github\np3\Elli\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE35B38-E8D9-4495-A590-10B0BAFEA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="student_results" sheetId="1" r:id="rId1"/>
     <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="114">
   <si>
     <t>student_id</t>
   </si>
@@ -290,19 +284,16 @@
     <t>beginner</t>
   </si>
   <si>
-    <t>Δημιουργήστε το αρχείο unique_elements.py, ορίστε μέσα τη συνάρτηση pop_out(a) που διατρέχει τη λίστα και προσθέτει σε μια νέα λίστα μόνο τα στοιχεία που δεν υπάρχουν ήδη σε αυτήν, και στη συνέχεια καλέστε την από το κύριο πρόγραμμά σας.</t>
-  </si>
-  <si>
-    <t>Διόρθωσε το συντακτικό σφάλμα στον κώδικά σου και βεβαιώσου ότι η συνάρτηση pop_out επιστρέφει τη νέα λίστα χωρίς διπλότυπα στοιχεία.</t>
-  </si>
-  <si>
-    <t>[{"title": "Python Modules Tutorial", "description": "Εισαγωγή δημιουργίας και χρήσης modules στην Python."}, {"title": "Python List Methods - append() and in operator", "description": "Πώς να προσθέτετε στοιχεία σε λίστα και να ελέγχετε αν ένα στοιχείο υπάρχει ήδη."}]</t>
-  </si>
-  <si>
-    <t>["Βασικοί κανόνες σύνταξης και στοίχισης (indentation) στην Python", "Ορισμός συναρτήσεων (def) και επιστροφή τιμών (return)", "Χρήση μεθόδων λιστών (π.χ. append, τελεστής in/not in)"]</t>
-  </si>
-  <si>
-    <t>ok</t>
+    <t>Δοκίμασε τον κώδικα με μία πολύ μικρή είσοδο και κατέγραψε τις τιμές.</t>
+  </si>
+  <si>
+    <t>Διόρθωσε πρώτα μία μικρή εκδοχή του ίδιου συντακτικού λάθους.</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>agent_error: ServerError: 503 UNAVAILABLE. {'error': {'code': 503, 'message': 'This model is currently experiencing high demand. Spikes in demand are usually temporary. Please try again later.', 'status': 'UNAVAILABLE'}}</t>
   </si>
   <si>
     <t>λίγα δεδομένα</t>
@@ -371,8 +362,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,21 +413,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -474,7 +457,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -508,7 +491,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -543,10 +525,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,17 +700,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BK3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="55" max="55" width="88.7109375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="68.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="230.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="248.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:63">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -920,7 +895,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:63">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1084,19 +1059,19 @@
         <v>91</v>
       </c>
       <c r="BH2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>93</v>
       </c>
-      <c r="BI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>94</v>
       </c>
-      <c r="BK2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:63">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1269,68 +1244,68 @@
         <v>90</v>
       </c>
       <c r="BG3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH3" t="s">
         <v>92</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BI3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>93</v>
       </c>
-      <c r="BI3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BJ3" t="s">
+      <c r="BK3" t="s">
         <v>94</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="BB2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="BB3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BB2" r:id="rId1"/>
+    <hyperlink ref="BB3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>98</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1338,73 +1313,73 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7">
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>103</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>104</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>105</v>
       </c>
-      <c r="B10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>107</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>108</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Elli/results_week_v5_resources.xlsx
+++ b/Elli/results_week_v5_resources.xlsx
@@ -209,13 +209,13 @@
     <t>ΈΧΈντριν Χεμπέγια</t>
   </si>
   <si>
-    <t>ΒΝΒΑΣΙΛ ΝΤΙΜΟ</t>
+    <t>test</t>
   </si>
   <si>
     <t>echempegia@uth.gr</t>
   </si>
   <si>
-    <t>vntimo@uth.gr</t>
+    <t>emarouda@outlook.com.gr</t>
   </si>
   <si>
     <t>generic_python</t>
@@ -224,7 +224,7 @@
     <t>SyntaxError</t>
   </si>
   <si>
-    <t>cannot assign to expression</t>
+    <t>invalid syntax</t>
   </si>
   <si>
     <t>syntax</t>
@@ -233,7 +233,7 @@
     <t>Δεν εντοπίστηκε συντακτικό λάθος.</t>
   </si>
   <si>
-    <t>Συντακτικό λάθος που χρειάζεται διόρθωση.</t>
+    <t>Γενικό συντακτικό λάθος.</t>
   </si>
   <si>
     <t>generic_needs_review</t>
@@ -278,7 +278,7 @@
     <t>Ποια είναι η τελευταία μεταβλητή ή συνάρτηση πριν από το runtime error;</t>
   </si>
   <si>
-    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 23;</t>
+    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 1;</t>
   </si>
   <si>
     <t>beginner</t>
@@ -1079,22 +1079,22 @@
         <v>66</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
         <v>67</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>68</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
         <v>69</v>
@@ -1193,10 +1193,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>232</v>
+        <v>379</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR3">
         <v>1</v>
